--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T2_0.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2019_T2_0.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="74">
   <si>
     <t/>
   </si>
@@ -30,15 +30,15 @@
     <t>personas_por_hogar_2007_localida</t>
   </si>
   <si>
+    <t>log_expenditure</t>
+  </si>
+  <si>
     <t>num_est_transmi</t>
   </si>
   <si>
     <t>icv_2007_localidad</t>
   </si>
   <si>
-    <t>gasto_promedio_mensual_2007_loca</t>
-  </si>
-  <si>
     <t>estrato_mean</t>
   </si>
   <si>
@@ -51,16 +51,13 @@
     <t>accesibilidad_arterial_dummy</t>
   </si>
   <si>
-    <t xml:space="preserve">If the table includes missing values (.n, .o, .v etc.) see the Missing values section in the help file for the Stata command iebaltab for definitions of these values. Significance: ***=.01, **=.05, *=.1. Full user input as written by user: [iebaltab poblacion_urbana_2009 personas_por_localidad_2007 personas_por_hogar_2007_localida num_est_transmi icv_2007_localidad gasto_promedio_mensual_2007_loca estrato_mean acceso_transmi accesibilidad_arterial accesibilidad_arterial_dummy, groupvar(dummy_oxxo) control(0) savexlsx(difmedias_controles_baselines_fixed_2019_T2_0) replace] </t>
+    <t xml:space="preserve">If the table includes missing values (.n, .o, .v etc.) see the Missing values section in the help file for the Stata command iebaltab for definitions of these values. Significance: ***=.01, **=.05, *=.1. Full user input as written by user: [iebaltab poblacion_urbana_2009 personas_por_localidad_2007 personas_por_hogar_2007_localida log_expenditure num_est_transmi icv_2007_localidad estrato_mean acceso_transmi accesibilidad_arterial accesibilidad_arterial_dummy, groupvar(dummy_oxxo) control(0) savexlsx(difmedias_controles_baselines_fixed_2019_T2_0) replace] </t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>81</t>
+    <t>78</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.61e+05</t>
-  </si>
-  <si>
-    <t>(65822.607)</t>
-  </si>
-  <si>
-    <t>494.233</t>
-  </si>
-  <si>
-    <t>(33.939)</t>
-  </si>
-  <si>
-    <t>3.583</t>
-  </si>
-  <si>
-    <t>(0.045)</t>
-  </si>
-  <si>
-    <t>11.634</t>
-  </si>
-  <si>
-    <t>(1.815)</t>
-  </si>
-  <si>
-    <t>88.750</t>
-  </si>
-  <si>
-    <t>(0.454)</t>
-  </si>
-  <si>
-    <t>1.08e+06</t>
-  </si>
-  <si>
-    <t>(53579.033)</t>
-  </si>
-  <si>
-    <t>2.583</t>
-  </si>
-  <si>
-    <t>(0.121)</t>
-  </si>
-  <si>
-    <t>3.537</t>
-  </si>
-  <si>
-    <t>(0.428)</t>
-  </si>
-  <si>
-    <t>33.878</t>
-  </si>
-  <si>
-    <t>(3.332)</t>
-  </si>
-  <si>
-    <t>0.976</t>
-  </si>
-  <si>
-    <t>(0.017)</t>
+    <t>5.80e+05</t>
+  </si>
+  <si>
+    <t>(68031.654)</t>
+  </si>
+  <si>
+    <t>499.835</t>
+  </si>
+  <si>
+    <t>(35.437)</t>
+  </si>
+  <si>
+    <t>3.566</t>
+  </si>
+  <si>
+    <t>(0.046)</t>
+  </si>
+  <si>
+    <t>13.810</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>12.192</t>
+  </si>
+  <si>
+    <t>(1.886)</t>
+  </si>
+  <si>
+    <t>88.950</t>
+  </si>
+  <si>
+    <t>(0.459)</t>
+  </si>
+  <si>
+    <t>2.617</t>
+  </si>
+  <si>
+    <t>(0.122)</t>
+  </si>
+  <si>
+    <t>3.679</t>
+  </si>
+  <si>
+    <t>(0.443)</t>
+  </si>
+  <si>
+    <t>33.064</t>
+  </si>
+  <si>
+    <t>(2.923)</t>
+  </si>
+  <si>
+    <t>0.987</t>
+  </si>
+  <si>
+    <t>(0.013)</t>
   </si>
   <si>
     <t>32</t>
@@ -159,6 +156,9 @@
     <t>(0.064)</t>
   </si>
   <si>
+    <t>14.066</t>
+  </si>
+  <si>
     <t>28.281</t>
   </si>
   <si>
@@ -171,12 +171,6 @@
     <t>(0.529)</t>
   </si>
   <si>
-    <t>1.36e+06</t>
-  </si>
-  <si>
-    <t>(79662.261)</t>
-  </si>
-  <si>
     <t>3.392</t>
   </si>
   <si>
@@ -201,10 +195,7 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>113</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -216,34 +207,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>2.25e+05</t>
-  </si>
-  <si>
-    <t>5.447</t>
-  </si>
-  <si>
-    <t>-0.265***</t>
-  </si>
-  <si>
-    <t>16.647***</t>
-  </si>
-  <si>
-    <t>2.486***</t>
-  </si>
-  <si>
-    <t>2.86e+05***</t>
-  </si>
-  <si>
-    <t>0.809***</t>
-  </si>
-  <si>
-    <t>2.870***</t>
-  </si>
-  <si>
-    <t>13.434**</t>
-  </si>
-  <si>
-    <t>0.024</t>
+    <t>2.06e+05</t>
+  </si>
+  <si>
+    <t>-0.155</t>
+  </si>
+  <si>
+    <t>-0.248***</t>
+  </si>
+  <si>
+    <t>0.257***</t>
+  </si>
+  <si>
+    <t>16.089***</t>
+  </si>
+  <si>
+    <t>2.285***</t>
+  </si>
+  <si>
+    <t>0.775***</t>
+  </si>
+  <si>
+    <t>2.727***</t>
+  </si>
+  <si>
+    <t>14.248***</t>
+  </si>
+  <si>
+    <t>0.013</t>
   </si>
 </sst>
 </file>
@@ -298,19 +289,19 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
@@ -321,19 +312,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
@@ -344,19 +335,19 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -367,19 +358,19 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -390,13 +381,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -413,19 +404,19 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -436,13 +427,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -459,19 +450,19 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -482,13 +473,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -505,19 +496,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
@@ -528,13 +519,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -551,19 +542,19 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -574,13 +565,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -597,19 +588,19 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +611,13 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
@@ -640,22 +631,22 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
@@ -666,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
         <v>0</v>
@@ -689,19 +680,19 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
@@ -712,13 +703,13 @@
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
@@ -735,19 +726,19 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -758,13 +749,13 @@
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
         <v>0</v>
@@ -781,19 +772,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
@@ -804,13 +795,13 @@
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F23" t="s">
         <v>0</v>
